--- a/data/trans_dic/DCD_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,23; 32,32</t>
+          <t>25,4; 32,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,71; 50,41</t>
+          <t>44,79; 50,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,69; 42,17</t>
+          <t>37,64; 42,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,39</t>
+          <t>7,81; 13,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 23,16</t>
+          <t>15,35; 23,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 17,68</t>
+          <t>12,6; 17,72</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,7</t>
+          <t>6,49; 10,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 23,04</t>
+          <t>17,57; 23,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,75; 16,19</t>
+          <t>12,8; 16,34</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,0</t>
+          <t>10,61; 14,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 28,11</t>
+          <t>21,01; 28,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 21,38</t>
+          <t>17,28; 21,36</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>129935; 166436</t>
+          <t>130784; 166054</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>337774; 380839</t>
+          <t>338406; 381466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>478853; 535781</t>
+          <t>478189; 533562</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>186435; 306627</t>
+          <t>178842; 300416</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>328526; 518303</t>
+          <t>343442; 520280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>561287; 800648</t>
+          <t>570704; 802515</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42100; 69208</t>
+          <t>41952; 68137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>115474; 152161</t>
+          <t>116010; 152992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166714; 211607</t>
+          <t>167349; 213624</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>366010; 517940</t>
+          <t>366213; 515891</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>755886; 1027227</t>
+          <t>767509; 1031369</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1235251; 1519430</t>
+          <t>1227786; 1517951</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,4; 32,25</t>
+          <t>23,82; 30,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,79; 50,49</t>
+          <t>44,37; 49,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,64; 42,0</t>
+          <t>36,7; 41,15</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,12</t>
+          <t>11,13; 13,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,35; 23,25</t>
+          <t>21,84; 25,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,72</t>
+          <t>16,82; 19,14</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,54</t>
+          <t>6,48; 10,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 23,16</t>
+          <t>18,38; 23,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 16,34</t>
+          <t>13,05; 16,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 14,95</t>
+          <t>12,9; 15,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,01; 28,23</t>
+          <t>26,9; 29,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 21,36</t>
+          <t>20,46; 22,15</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>147842</t>
+          <t>158391</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>359163</t>
+          <t>386033</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>507006</t>
+          <t>544423</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>130784; 166054</t>
+          <t>137777; 178088</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>338406; 381466</t>
+          <t>364732; 407236</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>478189; 533562</t>
+          <t>513982; 576379</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>259870</t>
+          <t>277829</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>454141</t>
+          <t>508478</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>714010</t>
+          <t>786307</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>178842; 300416</t>
+          <t>248206; 312129</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>343442; 520280</t>
+          <t>474293; 548126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>570704; 802515</t>
+          <t>740555; 842750</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54868</t>
+          <t>60118</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>153639</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189130</t>
+          <t>213758</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41952; 68137</t>
+          <t>46087; 75100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116010; 152992</t>
+          <t>135076; 175375</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>167349; 213624</t>
+          <t>188792; 241525</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>947567</t>
+          <t>1048151</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1410147</t>
+          <t>1544489</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>366213; 515891</t>
+          <t>454333; 538621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>767509; 1031369</t>
+          <t>1002854; 1095352</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1227786; 1517951</t>
+          <t>1483039; 1605829</t>
         </is>
       </c>
     </row>
